--- a/tmp/mam3-2025-26-s5.xlsx
+++ b/tmp/mam3-2025-26-s5.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="556">
   <si>
     <t>Rappel du bulletin</t>
   </si>
@@ -4754,7 +4754,7 @@
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="A44" s="20" t="s">
         <v>323</v>
       </c>
       <c r="B44" t="s">
